--- a/Fixed_Assets_Depreciation_Schedule.xlsx
+++ b/Fixed_Assets_Depreciation_Schedule.xlsx
@@ -7,9 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Asset Register" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Depreciation Charge" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Method &amp; Correction" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Asset Register (detail)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Method &amp; Correction" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,7 +33,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="001A1A1A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -43,6 +41,11 @@
       <sz val="9.5"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10.5"/>
+    </font>
+    <font>
       <sz val="9.5"/>
     </font>
     <font>
@@ -51,9 +54,31 @@
     </font>
     <font>
       <name val="Consolas"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
       <b val="1"/>
-      <color rgb="00B02A1A"/>
+      <color rgb="001E7A46"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9.5"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -63,28 +88,22 @@
       <name val="Consolas"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="007a2a12"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
     <font>
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="10"/>
     </font>
+    <font>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -103,7 +122,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F4F8"/>
+        <fgColor rgb="007A1F2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBF6EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDF1F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -113,12 +142,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FBF3EC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007A1F2B"/>
+        <fgColor rgb="00F2F4F8"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -160,58 +184,64 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -579,250 +609,763 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>سجل الأصول الثابتة والإهلاك</t>
+          <t>سجل الأصول الثابتة والإهلاك — تفصيل أصل-أصل (بعد إعادة الحساب)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fixed Asset Register &amp; Depreciation Schedule   ·   Al Marwa Projects — Audit Dept. — 11 Oct 2026   ·   Currency: QAR</t>
+          <t>Fixed Asset Register &amp; Depreciation — asset-by-asset (recomputed, straight-line, as of 30/09/2026) · Al Marwa Projects · QAR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>البند / النوع — Category / Asset type</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>البند / Category</t>
+          <t>العمر (شهر)
+Life</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>الحسابات
-Accounts</t>
+          <t>العدد
+Qty</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>العمر (شهر)
-Useful life (m)</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>التكلفة
 Cost</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>مجمّع الإهلاك
 Accum. Depr.</t>
         </is>
       </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>صافي القيمة
+NBV</t>
+        </is>
+      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>ص.ق.د كما هو مُثبت
-NBV (recorded)</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>ص.ق.د المحمولة
-Carrying NBV (floor 0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
+          <t>نسبة الإهلاك
+% Depr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>①</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>سيارات ومركبات — Motor Vehicles</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>100609 / 100601</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
+          <t>① سيارات ومركبات — Motor Vehicles    —    100609 / 100601</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="16" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Vehicles — سيارات</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="C6" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>671601</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>671601</v>
+      </c>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي / غير مُسجّل بالوحدة — Opening / unregistered</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="11" t="inlineStr"/>
+      <c r="D7" s="12" t="n">
+        <v>214810</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>108654.32</v>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>106155.68</v>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>50.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>إجمالي البند — Subtotal</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="inlineStr"/>
+      <c r="C8" s="15" t="inlineStr"/>
+      <c r="D8" s="16" t="n">
         <v>886411</v>
       </c>
-      <c r="F5" s="6" t="n">
-        <v>-780255.3199999999</v>
-      </c>
-      <c r="G5" s="6" t="n">
-        <v>106155.6800000001</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>106155.6800000001</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>②</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>تقنية وإلكترونيات — IT, Electronics &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>100605 / 100607</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
+      <c r="E8" s="16" t="n">
+        <v>780255.3199999999</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>106155.68</v>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>88.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>② تقنية وإلكترونيات — IT, Electronics &amp; Equipment    —    100605 / 100607</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Computer &amp; Accessories — كمبيوتر وملحقات</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="E6" s="9" t="n">
+      <c r="C10" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>80721</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>78971.86</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>1749.14</v>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>97.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Camera &amp; CCTV — كاميرات ومراقبة</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>111740</v>
+      </c>
+      <c r="E11" s="8" t="n">
+        <v>111740</v>
+      </c>
+      <c r="F11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Mobile &amp; Accessories — موبايل وملحقات</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>33189</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>33189</v>
+      </c>
+      <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Office Printer — طابعات مكتب</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="8" t="n">
+        <v>22982</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>10985.8</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>11996.2</v>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>47.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Shop Printers (POS) — طابعات نقاط بيع</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" s="8" t="n">
+        <v>18100</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>17238.9</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>861.1</v>
+      </c>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>95.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Barcode Scanner — أجهزة باركود</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="8" t="n">
+        <v>27565</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>27565</v>
+      </c>
+      <c r="F15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="16" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي / غير مُسجّل — Opening / unregistered</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr"/>
+      <c r="D16" s="12" t="n">
+        <v>67193</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>67193</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>إجمالي البند — Subtotal</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr"/>
+      <c r="C17" s="15" t="inlineStr"/>
+      <c r="D17" s="16" t="n">
         <v>361490</v>
       </c>
-      <c r="F6" s="9" t="n">
-        <v>-471061</v>
-      </c>
-      <c r="G6" s="10" t="n">
-        <v>-109571</v>
-      </c>
-      <c r="H6" s="9" t="n">
+      <c r="E17" s="16" t="n">
+        <v>346883.56</v>
+      </c>
+      <c r="F17" s="16" t="n">
+        <v>14606.44</v>
+      </c>
+      <c r="G17" s="17" t="inlineStr">
+        <is>
+          <t>96.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>③ آلات ومعدات وأجهزة — Machinery, Equipment &amp; Appliances    —    100720 / 100740</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>AC Air Condition — تكييفات</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>63</v>
+      </c>
+      <c r="D19" s="8" t="n">
+        <v>200168</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>198548</v>
+      </c>
+      <c r="F19" s="18" t="n">
+        <v>1620</v>
+      </c>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>99.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Fork Lift — رافعة شوكية</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>120</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="8" t="n">
+        <v>56250</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>56250</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>③</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>آلات ومعدات وأجهزة — Machinery, Equipment &amp; Appliances</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>100720 / 100740</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Furniture &amp; Equipment — أثاث ومعدات</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="D21" s="8" t="n">
+        <v>47330.5</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>47330.5</v>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Generator — مولّد كهرباء</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="C22" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>14400</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Refrigerator — ثلاجات</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C23" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="8" t="n">
+        <v>9138</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>9138</v>
+      </c>
+      <c r="F23" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Washing Machine — غسالات</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>9406</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>9406</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Scale for Store — موازين</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>2250</v>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Trolly — عربات</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي / غير مُسجّل — Opening / unregistered</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr"/>
+      <c r="D27" s="12" t="n">
+        <v>17172.5</v>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>17172.5</v>
+      </c>
+      <c r="F27" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>إجمالي البند — Subtotal</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr"/>
+      <c r="C28" s="15" t="inlineStr"/>
+      <c r="D28" s="16" t="n">
         <v>358615</v>
       </c>
-      <c r="F7" s="6" t="n">
-        <v>-393050.44</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>-34435.44</v>
-      </c>
-      <c r="H7" s="6" t="n">
+      <c r="E28" s="16" t="n">
+        <v>356995</v>
+      </c>
+      <c r="F28" s="16" t="n">
+        <v>1620</v>
+      </c>
+      <c r="G28" s="17" t="inlineStr">
+        <is>
+          <t>99.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>④ أصول ثابتة عامة — General Fixed Assets    —    100604 / 100606</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي (غير محدّد) — Opening balance (unidentified)</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr"/>
+      <c r="D30" s="12" t="n">
+        <v>73520.5</v>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>73520.5</v>
+      </c>
+      <c r="F30" s="12" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>④</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>أصول ثابتة عامة — General Fixed Assets</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>100604 / 100606</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>120</v>
-      </c>
-      <c r="E8" s="9" t="n">
+      <c r="G30" s="14" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="15" t="inlineStr">
+        <is>
+          <t>إجمالي البند — Subtotal</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr"/>
+      <c r="C31" s="15" t="inlineStr"/>
+      <c r="D31" s="16" t="n">
         <v>73520.5</v>
       </c>
-      <c r="F8" s="9" t="n">
-        <v>-74929.47</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>-1408.970000000001</v>
-      </c>
-      <c r="H8" s="9" t="n">
+      <c r="E31" s="16" t="n">
+        <v>73520.5</v>
+      </c>
+      <c r="F31" s="16" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>الإجمالي / TOTAL</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="13" t="n">
+      <c r="G31" s="17" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>الإجمالي العام — GRAND TOTAL</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr"/>
+      <c r="C32" s="19" t="inlineStr"/>
+      <c r="D32" s="20" t="n">
         <v>1680036.5</v>
       </c>
-      <c r="F9" s="13" t="n">
-        <v>-1719296.23</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>-39259.72999999975</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>106155.6800000001</v>
-      </c>
-    </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>مجمّع إهلاك زائد عن التكلفة (البنود ②③④) = 145,415.41 ر.ق — صافي الأثر بعد السيارات الموجبة = (39,259.73). السبب: إهلاك الأصول على ~5 أشهر بدل أعمارها الإنتاجية. عُولِج الجزء الأكبر بقيد SLX-DEPR (363,670.35) مدين المجمّع / دائن الأرباح المُرحّلة؛ والمتبقّي يُستكمل عند تصحيح الأعمار الإنتاجية (method_number) وإعادة توليد جداول الإهلاك — عمل المحاسب.</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
+      <c r="E32" s="20" t="n">
+        <v>1557654.38</v>
+      </c>
+      <c r="F32" s="20" t="n">
+        <v>122382.12</v>
+      </c>
+      <c r="G32" s="21" t="inlineStr">
+        <is>
+          <t>92.7%</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="6">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -834,268 +1377,106 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>مصروف الإهلاك المُحمّل (قائمة الدخل)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Depreciation Charge for the Period (P&amp;L)   ·   Al Marwa Projects — Audit Dept. — 11 Oct 2026   ·   Currency: QAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>الكود
-Code</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="inlineStr">
-        <is>
-          <t>حساب المصروف / Expense account</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="inlineStr">
-        <is>
-          <t>المبلغ
-Amount</t>
-        </is>
-      </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>البند المقابل / Maps to</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
-        <is>
-          <t>500803</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Depreciation of Motor Vehicles</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>671601</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>① سيارات</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>500805</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>Depreciation Expense - IT &amp; Electronics</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>78622</v>
-      </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>② تقنية</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>500804</t>
-        </is>
-      </c>
-      <c r="B7" s="18" t="inlineStr">
-        <is>
-          <t>Depreciation Expense - Furniture</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>58785.5</v>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>③/④ أثاث ومعدات</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>502038</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>Depreciation Expenses (General)</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>492505</v>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>عام / موزّع</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>الإجمالي / TOTAL</t>
-        </is>
-      </c>
-      <c r="C9" s="21" t="n">
-        <v>1301513.5</v>
-      </c>
-      <c r="D9" s="12" t="inlineStr"/>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>طريقة إعادة الحساب وقيود التصحيح</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="34" customHeight="1">
+      <c r="A3" s="23" t="inlineStr">
+        <is>
+          <t>طريقة الإهلاك / Method</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>القسط الثابت (Straight-line) — شهري، من جدول كل أصل في وحدة الأصول</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>تاريخ التقرير / As of</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>30/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>إعادة الحساب / Recompute</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>مجمّع إهلاك كل أصل = قيمته ÷ عمره الإنتاجي × الأشهر المنقضية، بسقف التكلفة (صافي ≥ صفر)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>قيد 1 / Entry 1</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>SLX-DEPR — MISC/2026/10/0019 — عكس إهلاك زائد 363,670.35 (مدين المجمّع / دائن 300101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>قيد 2 / Entry 2</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>SLX-DEPR-RECALC — 11/10/2026 — تعديل المجمّع للرصيد الصحيح 161,641.85 (مدين المجمّع / دائن 300101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>قاعدة / Rule</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>مجمّع الإهلاك ≤ التكلفة لكل أصل دائمًا — صافي القيمة الدفترية ≥ صفر</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>ملاحظة / Note</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>القيد الافتتاحي 34200 لم يُمَس · العملية قابلة للعكس · تصحيح الأعمار وإعادة توليد الجداول عمل المحاسب</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="78" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>السياسة والتصحيح</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Depreciation Policy &amp; Correction Entry   ·   Al Marwa Projects — Audit Dept. — 11 Oct 2026   ·   Currency: QAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>طريقة الإهلاك / Method</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>القسط الثابت (Straight-line) — شهري</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>الأعمار الإنتاجية / Useful lives</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr">
-        <is>
-          <t>سيارات 60 شهر (5 سنوات) · تقنية وإلكترونيات 36 شهر (3 سنوات) · آلات/أثاث/عام 120 شهر (10 سنوات)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>العملة / Currency</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>ريال قطري (QAR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="22" t="inlineStr">
-        <is>
-          <t>تاريخ الكشف / As of</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>11/10/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>قيد التصحيح / Correction</t>
-        </is>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>SLX-DEPR — MISC/2026/10/0019 — 07/10/2026 — عكس إهلاك زائد 363,670.35 (مدين مجمّع الإهلاك / دائن 300101 أرباح مُرحّلة)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="22" t="inlineStr">
-        <is>
-          <t>المتبقّي / Residual</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>تصحيح method_number للأصول وإعادة توليد جداول الإهلاك — ليستكمله المحاسب</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="34" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>ملاحظة / Note</t>
-        </is>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>وحدة Asset Management غير مُفعّلة؛ الأصول تُدار بحسابات دفترية. لا مساس بالقيد الافتتاحي 34200.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Fixed_Assets_Depreciation_Schedule.xlsx
+++ b/Fixed_Assets_Depreciation_Schedule.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Asset Register (detail)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Asset Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Method &amp; Correction" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -54,14 +54,14 @@
     </font>
     <font>
       <name val="Consolas"/>
-      <color rgb="00666666"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
       <b val="1"/>
       <color rgb="001E7A46"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -196,7 +196,10 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,10 +211,7 @@
     <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -222,9 +222,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -613,25 +610,25 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>سجل الأصول الثابتة والإهلاك — تفصيل أصل-أصل (بعد إعادة الحساب)</t>
+          <t>سجل الأصول الثابتة والإهلاك — ملخّص بالبند (بعد إعادة الحساب الصحيح)</t>
         </is>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fixed Asset Register &amp; Depreciation — asset-by-asset (recomputed, straight-line, as of 30/09/2026) · Al Marwa Projects · QAR</t>
+          <t>Fixed Asset Register &amp; Depreciation — summary (recomputed, correct useful life, as of 30/09/2026) · Al Marwa Projects · QAR</t>
         </is>
       </c>
     </row>
@@ -643,8 +640,8 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>العمر (شهر)
-Life</t>
+          <t>العمر
+Life(m)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -662,7 +659,7 @@
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>مجمّع الإهلاك
-Accum. Depr.</t>
+Accum.</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
@@ -673,8 +670,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>نسبة الإهلاك
-% Depr.</t>
+          <t>% إهلاك</t>
         </is>
       </c>
     </row>
@@ -707,41 +703,41 @@
         <v>671601</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>671601</v>
-      </c>
-      <c r="F6" s="8" t="n">
+        <v>435032.18</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>236568.82</v>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>64.8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>رصيد افتتاحي / غير مُسجّل — Opening / unregistered</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr"/>
+      <c r="D7" s="13" t="n">
+        <v>214810</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>214810</v>
+      </c>
+      <c r="F7" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>100.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>رصيد افتتاحي / غير مُسجّل بالوحدة — Opening / unregistered</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr"/>
-      <c r="D7" s="12" t="n">
-        <v>214810</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>108654.32</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>106155.68</v>
-      </c>
-      <c r="G7" s="14" t="inlineStr">
-        <is>
-          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -757,14 +753,14 @@
         <v>886411</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>780255.3199999999</v>
+        <v>649842.1800000001</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>106155.68</v>
+        <v>236568.82</v>
       </c>
       <c r="G8" s="17" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
     </row>
@@ -784,54 +780,54 @@
     <row r="10" ht="16" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Computer &amp; Accessories — كمبيوتر وملحقات</t>
+          <t>Camera &amp; CCTV — كاميرات ومراقبة</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D10" s="8" t="n">
-        <v>80721</v>
+        <v>111740</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>78971.86</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>1749.14</v>
-      </c>
-      <c r="G10" s="9" t="inlineStr">
-        <is>
-          <t>97.8%</t>
+        <v>82098</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>29642</v>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>73.5%</t>
         </is>
       </c>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Camera &amp; CCTV — كاميرات ومراقبة</t>
+          <t>Computer &amp; Accessories — كمبيوتر وملحقات</t>
         </is>
       </c>
       <c r="B11" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="C11" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="C11" s="7" t="n">
-        <v>20</v>
-      </c>
       <c r="D11" s="8" t="n">
-        <v>111740</v>
+        <v>80721</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>111740</v>
-      </c>
-      <c r="F11" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>73219.08</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>7501.92</v>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>90.7%</t>
         </is>
       </c>
     </row>
@@ -851,117 +847,117 @@
         <v>33189</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>33189</v>
-      </c>
-      <c r="F12" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>31248.28</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>1940.72</v>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>94.2%</t>
         </is>
       </c>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>Office Printer — طابعات مكتب</t>
+          <t>Barcode Scanner — أجهزة باركود</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
         <v>36</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>22982</v>
+        <v>27565</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>10985.8</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>11996.2</v>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>47.8%</t>
+        <v>26876.11</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>688.89</v>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>97.5%</t>
         </is>
       </c>
     </row>
     <row r="14" ht="16" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>Shop Printers (POS) — طابعات نقاط بيع</t>
+          <t>Office Printer — طابعات مكتب</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
         <v>36</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="D14" s="8" t="n">
-        <v>18100</v>
+        <v>22982</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>17238.9</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>861.1</v>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>95.2%</t>
+        <v>9992.709999999999</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>12989.29</v>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
+        <is>
+          <t>43.5%</t>
         </is>
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Barcode Scanner — أجهزة باركود</t>
+          <t>Shop Printers (POS) — طابعات نقاط بيع</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
         <v>36</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D15" s="8" t="n">
-        <v>27565</v>
+        <v>18100</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>27565</v>
-      </c>
-      <c r="F15" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>17211.12</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>888.88</v>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
+        <is>
+          <t>95.1%</t>
         </is>
       </c>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>رصيد افتتاحي / غير مُسجّل — Opening / unregistered</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
+      <c r="C16" s="12" t="inlineStr"/>
+      <c r="D16" s="13" t="n">
         <v>67193</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="13" t="n">
         <v>67193</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="F16" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -982,14 +978,14 @@
         <v>361490</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>346883.56</v>
+        <v>307838.3</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>14606.44</v>
+        <v>53651.7</v>
       </c>
       <c r="G17" s="17" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>85.2%</t>
         </is>
       </c>
     </row>
@@ -1022,14 +1018,14 @@
         <v>200168</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>198548</v>
-      </c>
-      <c r="F19" s="18" t="n">
-        <v>1620</v>
-      </c>
-      <c r="G19" s="9" t="inlineStr">
-        <is>
-          <t>99.2%</t>
+        <v>168060.91</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>32107.09</v>
+      </c>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>84.0%</t>
         </is>
       </c>
     </row>
@@ -1049,14 +1045,14 @@
         <v>56250</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>56250</v>
-      </c>
-      <c r="F20" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>15020.84</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>41229.16</v>
+      </c>
+      <c r="G20" s="10" t="inlineStr">
+        <is>
+          <t>26.7%</t>
         </is>
       </c>
     </row>
@@ -1076,14 +1072,14 @@
         <v>47330.5</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>47330.5</v>
-      </c>
-      <c r="F21" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>37001.43</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>10329.07</v>
+      </c>
+      <c r="G21" s="10" t="inlineStr">
+        <is>
+          <t>78.2%</t>
         </is>
       </c>
     </row>
@@ -1103,75 +1099,75 @@
         <v>14400</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>14400</v>
-      </c>
-      <c r="F22" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>6192.5</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>8207.5</v>
+      </c>
+      <c r="G22" s="10" t="inlineStr">
+        <is>
+          <t>43.0%</t>
         </is>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>Refrigerator — ثلاجات</t>
+          <t>Washing Machine — غسالات</t>
         </is>
       </c>
       <c r="B23" s="7" t="n">
         <v>60</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="8" t="n">
-        <v>9138</v>
+        <v>9406</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9138</v>
-      </c>
-      <c r="F23" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>4426.38</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>4979.62</v>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Washing Machine — غسالات</t>
+          <t>Refrigerator — ثلاجات</t>
         </is>
       </c>
       <c r="B24" s="7" t="n">
         <v>60</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>9406</v>
+        <v>9138</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>9406</v>
-      </c>
-      <c r="F24" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>4178.21</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>4959.79</v>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>45.7%</t>
         </is>
       </c>
     </row>
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>Scale for Store — موازين</t>
+          <t>Trolly — عربات</t>
         </is>
       </c>
       <c r="B25" s="7" t="n">
@@ -1181,24 +1177,24 @@
         <v>1</v>
       </c>
       <c r="D25" s="8" t="n">
-        <v>2250</v>
+        <v>2500</v>
       </c>
       <c r="E25" s="8" t="n">
-        <v>2250</v>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+        <v>1000</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>Trolly — عربات</t>
+          <t>Scale for Store — موازين</t>
         </is>
       </c>
       <c r="B26" s="7" t="n">
@@ -1208,39 +1204,39 @@
         <v>1</v>
       </c>
       <c r="D26" s="8" t="n">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>2500</v>
+        <v>2250</v>
       </c>
       <c r="F26" s="8" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>رصيد افتتاحي / غير مُسجّل — Opening / unregistered</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr"/>
-      <c r="D27" s="12" t="n">
+      <c r="C27" s="12" t="inlineStr"/>
+      <c r="D27" s="13" t="n">
         <v>17172.5</v>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="13" t="n">
         <v>17172.5</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="F27" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -1261,14 +1257,14 @@
         <v>358615</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>356995</v>
+        <v>255302.77</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>1620</v>
+        <v>103312.23</v>
       </c>
       <c r="G28" s="17" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>71.2%</t>
         </is>
       </c>
     </row>
@@ -1286,24 +1282,24 @@
       <c r="G29" s="5" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="10" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>رصيد افتتاحي (غير محدّد) — Opening balance (unidentified)</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C30" s="11" t="inlineStr"/>
-      <c r="D30" s="12" t="n">
+      <c r="C30" s="12" t="inlineStr"/>
+      <c r="D30" s="13" t="n">
         <v>73520.5</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="13" t="n">
         <v>73520.5</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="F30" s="13" t="n">
         <v>0</v>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -1336,25 +1332,25 @@
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>الإجمالي العام — GRAND TOTAL</t>
         </is>
       </c>
-      <c r="B32" s="19" t="inlineStr"/>
-      <c r="C32" s="19" t="inlineStr"/>
-      <c r="D32" s="20" t="n">
+      <c r="B32" s="18" t="inlineStr"/>
+      <c r="C32" s="18" t="inlineStr"/>
+      <c r="D32" s="19" t="n">
         <v>1680036.5</v>
       </c>
-      <c r="E32" s="20" t="n">
-        <v>1557654.38</v>
-      </c>
-      <c r="F32" s="20" t="n">
-        <v>122382.12</v>
-      </c>
-      <c r="G32" s="21" t="inlineStr">
-        <is>
-          <t>92.7%</t>
+      <c r="E32" s="19" t="n">
+        <v>1286503.75</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>393532.75</v>
+      </c>
+      <c r="G32" s="20" t="inlineStr">
+        <is>
+          <t>76.6%</t>
         </is>
       </c>
     </row>
@@ -1377,101 +1373,113 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="82" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="21" t="inlineStr">
         <is>
           <t>طريقة إعادة الحساب وقيود التصحيح</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="22" t="inlineStr">
         <is>
           <t>طريقة الإهلاك / Method</t>
         </is>
       </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>القسط الثابت (Straight-line) — شهري، من جدول كل أصل في وحدة الأصول</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
-      <c r="A4" s="23" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
+        <is>
+          <t>القسط الثابت (Straight-line) — شهري</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="22" t="inlineStr">
+        <is>
+          <t>العمر الإنتاجي / Useful life</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>سيارات 60ش · تقنية 36-60ش · آلات/معدات 60-120ش (من فئة كل أصل)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>تاريخ التقرير / As of</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>30/09/2026</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>إعادة الحساب / Recompute</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="inlineStr">
-        <is>
-          <t>مجمّع إهلاك كل أصل = قيمته ÷ عمره الإنتاجي × الأشهر المنقضية، بسقف التكلفة (صافي ≥ صفر)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="34" customHeight="1">
-      <c r="A6" s="23" t="inlineStr">
-        <is>
-          <t>قيد 1 / Entry 1</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="inlineStr">
-        <is>
-          <t>SLX-DEPR — MISC/2026/10/0019 — عكس إهلاك زائد 363,670.35 (مدين المجمّع / دائن 300101)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="34" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>قيد 2 / Entry 2</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>SLX-DEPR-RECALC — 11/10/2026 — تعديل المجمّع للرصيد الصحيح 161,641.85 (مدين المجمّع / دائن 300101)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" s="23" t="inlineStr">
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>الأساس / Basis</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>تكلفة كل أصل × (الأشهر المنقضية من تاريخ الشراء ÷ العمر)، بسقف التكلفة</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>السبب / Root cause</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>كان العمر مُسجّلاً 5 أشهر بدل الحقيقي — أدّى لإهلاك كامل خاطئ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>القيد / Entry</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>SLX-DEPR-RECALC — 11/10/2026 — تعديل المجمّع للقيم الصحيحة (دائن 300101)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="22" t="inlineStr">
         <is>
           <t>قاعدة / Rule</t>
         </is>
       </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>مجمّع الإهلاك ≤ التكلفة لكل أصل دائمًا — صافي القيمة الدفترية ≥ صفر</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="34" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>مجمّع الإهلاك ≤ التكلفة لكل أصل — صافي القيمة ≥ صفر</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="22" t="inlineStr">
         <is>
           <t>ملاحظة / Note</t>
         </is>
       </c>
-      <c r="B9" s="24" t="inlineStr">
-        <is>
-          <t>القيد الافتتاحي 34200 لم يُمَس · العملية قابلة للعكس · تصحيح الأعمار وإعادة توليد الجداول عمل المحاسب</t>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>القيد الافتتاحي 34200 لم يُمَس · قابل للعكس · تصحيح الأعمار في الوحدة = عمل المحاسب</t>
         </is>
       </c>
     </row>
